--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6452" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6452" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,6 +1346,9 @@
 </t>
   </si>
   <si>
+    <t>In der Serologie ist ein praekoordiniertes Specimen ausdruecklich zulaessig — anders als in den uebrigen Bereichen dieses Moduls gilt die Konvention 'System = XXX' hier NICHT. Das europaeische Whitepaper begruendet die Ausnahme damit, dass in der Serologie nur wenige Materialien vorkommen, ueberwiegend Serum, und ein Code-Wildwuchs deshalb nicht droht.</t>
+  </si>
+  <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
   </si>
   <si>
@@ -2242,7 +2245,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -9825,16 +9828,16 @@
         <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>63</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9863,7 +9866,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>76</v>
@@ -9898,10 +9901,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9998,10 +10001,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10100,10 +10103,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10202,10 +10205,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10302,10 +10305,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10404,10 +10407,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10508,10 +10511,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10610,10 +10613,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10714,10 +10717,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10818,10 +10821,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10922,13 +10925,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>76</v>
@@ -10972,7 +10975,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10990,10 +10993,10 @@
         <v>141</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
@@ -11028,10 +11031,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11132,10 +11135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11158,19 +11161,19 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>76</v>
@@ -11219,7 +11222,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -11236,10 +11239,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11336,10 +11339,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11438,10 +11441,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11467,13 +11470,13 @@
         <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11523,7 +11526,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -11532,7 +11535,7 @@
         <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>91</v>
@@ -11540,10 +11543,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11569,13 +11572,13 @@
         <v>125</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11604,10 +11607,10 @@
         <v>141</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11625,7 +11628,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11642,10 +11645,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11671,13 +11674,13 @@
         <v>258</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11727,7 +11730,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11744,10 +11747,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11773,13 +11776,13 @@
         <v>98</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11829,7 +11832,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11846,10 +11849,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11872,16 +11875,16 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11931,7 +11934,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11948,14 +11951,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11974,19 +11977,19 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>76</v>
@@ -12035,7 +12038,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -12052,10 +12055,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12152,10 +12155,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12254,10 +12257,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12283,13 +12286,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12339,7 +12342,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -12348,7 +12351,7 @@
         <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>91</v>
@@ -12356,10 +12359,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12385,13 +12388,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12420,10 +12423,10 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
@@ -12441,7 +12444,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -12458,10 +12461,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12487,13 +12490,13 @@
         <v>258</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12543,7 +12546,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
@@ -12560,10 +12563,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12589,13 +12592,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12645,7 +12648,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12662,14 +12665,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12688,19 +12691,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
@@ -12749,7 +12752,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12761,15 +12764,15 @@
         <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12866,10 +12869,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12968,13 +12971,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="B99" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="C99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>103</v>
@@ -12996,13 +12999,13 @@
         <v>76</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>107</v>
@@ -13072,10 +13075,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13098,13 +13101,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13155,7 +13158,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -13172,10 +13175,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13201,13 +13204,13 @@
         <v>119</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13257,7 +13260,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -13274,10 +13277,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13300,19 +13303,19 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>388</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -13361,7 +13364,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -13378,10 +13381,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13404,19 +13407,19 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -13453,17 +13456,17 @@
         <v>76</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -13472,7 +13475,7 @@
         <v>83</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>91</v>
@@ -13480,13 +13483,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -13508,19 +13511,19 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -13569,7 +13572,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -13578,7 +13581,7 @@
         <v>83</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>91</v>
@@ -13586,10 +13589,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13686,10 +13689,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13788,10 +13791,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13814,13 +13817,13 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13871,7 +13874,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -13888,10 +13891,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13988,10 +13991,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14090,10 +14093,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14116,19 +14119,19 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>76</v>
@@ -14177,7 +14180,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
@@ -14194,10 +14197,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14223,20 +14226,20 @@
         <v>159</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="R111" t="s" s="2">
         <v>76</v>
@@ -14260,10 +14263,10 @@
         <v>225</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>76</v>
@@ -14281,7 +14284,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -14298,10 +14301,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14327,14 +14330,14 @@
         <v>98</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -14383,7 +14386,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -14400,10 +14403,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14429,14 +14432,14 @@
         <v>125</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -14485,7 +14488,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -14494,7 +14497,7 @@
         <v>83</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>91</v>
@@ -14502,10 +14505,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14531,16 +14534,16 @@
         <v>159</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -14589,7 +14592,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -14606,10 +14609,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14632,13 +14635,13 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -14689,7 +14692,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14706,10 +14709,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14806,10 +14809,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14908,10 +14911,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14934,19 +14937,19 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>76</v>
@@ -14995,7 +14998,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -15012,10 +15015,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15041,20 +15044,20 @@
         <v>159</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q119" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="R119" t="s" s="2">
         <v>76</v>
@@ -15078,10 +15081,10 @@
         <v>225</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>76</v>
@@ -15099,7 +15102,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -15116,10 +15119,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15145,14 +15148,14 @@
         <v>98</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>76</v>
@@ -15201,7 +15204,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
@@ -15218,10 +15221,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15247,14 +15250,14 @@
         <v>125</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>76</v>
@@ -15303,7 +15306,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
@@ -15312,7 +15315,7 @@
         <v>83</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>91</v>
@@ -15320,10 +15323,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15349,16 +15352,16 @@
         <v>159</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -15407,7 +15410,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
@@ -15424,13 +15427,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>76</v>
@@ -15452,19 +15455,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>76</v>
@@ -15513,7 +15516,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -15522,7 +15525,7 @@
         <v>83</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>91</v>
@@ -15530,10 +15533,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15630,10 +15633,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15732,13 +15735,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>103</v>
@@ -15760,16 +15763,16 @@
         <v>76</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -15836,10 +15839,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15862,19 +15865,19 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
@@ -15923,7 +15926,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
@@ -15940,10 +15943,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16040,10 +16043,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16142,13 +16145,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="B130" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="C130" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>103</v>
@@ -16170,16 +16173,16 @@
         <v>76</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -16246,10 +16249,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16272,13 +16275,13 @@
         <v>76</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -16329,7 +16332,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -16346,10 +16349,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16375,22 +16378,22 @@
         <v>159</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="R132" t="s" s="2">
         <v>76</v>
@@ -16414,10 +16417,10 @@
         <v>225</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>76</v>
@@ -16435,7 +16438,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -16452,10 +16455,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16481,16 +16484,16 @@
         <v>98</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -16539,7 +16542,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -16556,10 +16559,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16585,23 +16588,23 @@
         <v>125</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>76</v>
@@ -16643,7 +16646,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16652,7 +16655,7 @@
         <v>83</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>91</v>
@@ -16660,10 +16663,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16689,16 +16692,16 @@
         <v>159</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16747,7 +16750,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16764,13 +16767,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>76</v>
@@ -16795,16 +16798,16 @@
         <v>282</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
@@ -16833,7 +16836,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
@@ -16851,7 +16854,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -16860,7 +16863,7 @@
         <v>83</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>91</v>
@@ -16868,10 +16871,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16968,10 +16971,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17070,10 +17073,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17174,10 +17177,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17274,10 +17277,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17376,10 +17379,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17480,10 +17483,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17582,10 +17585,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17686,10 +17689,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17790,10 +17793,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17894,10 +17897,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17998,13 +18001,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>76</v>
@@ -18026,19 +18029,19 @@
         <v>84</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>76</v>
@@ -18087,7 +18090,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -18096,7 +18099,7 @@
         <v>83</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>91</v>
@@ -18104,10 +18107,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18133,16 +18136,16 @@
         <v>282</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -18171,7 +18174,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>76</v>
@@ -18189,7 +18192,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
@@ -18198,7 +18201,7 @@
         <v>83</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>91</v>
@@ -18206,14 +18209,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -18235,16 +18238,16 @@
         <v>282</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>76</v>
@@ -18272,10 +18275,10 @@
         <v>141</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>76</v>
@@ -18293,7 +18296,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
@@ -18310,10 +18313,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18336,19 +18339,19 @@
         <v>76</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>76</v>
@@ -18397,7 +18400,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -18414,10 +18417,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18443,13 +18446,13 @@
         <v>282</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18478,10 +18481,10 @@
         <v>149</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>76</v>
@@ -18499,7 +18502,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -18516,10 +18519,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18545,16 +18548,16 @@
         <v>282</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>76</v>
@@ -18583,7 +18586,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>76</v>
@@ -18601,7 +18604,7 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>74</v>
@@ -18618,10 +18621,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18718,10 +18721,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18820,10 +18823,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18924,10 +18927,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19024,10 +19027,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19126,10 +19129,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19230,10 +19233,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19332,10 +19335,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19436,10 +19439,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19540,10 +19543,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19644,10 +19647,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19748,10 +19751,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19774,16 +19777,16 @@
         <v>76</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19833,7 +19836,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>74</v>
@@ -19850,10 +19853,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19950,10 +19953,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20052,10 +20055,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20081,13 +20084,13 @@
         <v>98</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -20137,7 +20140,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>74</v>
@@ -20146,7 +20149,7 @@
         <v>83</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>91</v>
@@ -20154,10 +20157,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20183,13 +20186,13 @@
         <v>125</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -20218,10 +20221,10 @@
         <v>141</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>76</v>
@@ -20239,7 +20242,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>74</v>
@@ -20256,10 +20259,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20285,13 +20288,13 @@
         <v>258</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20341,7 +20344,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>74</v>
@@ -20358,10 +20361,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20387,13 +20390,13 @@
         <v>98</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20443,7 +20446,7 @@
         <v>76</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>74</v>
@@ -20460,10 +20463,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20486,16 +20489,16 @@
         <v>76</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20545,7 +20548,7 @@
         <v>76</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>74</v>
@@ -20562,10 +20565,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20662,10 +20665,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20764,10 +20767,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20793,13 +20796,13 @@
         <v>98</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -20849,7 +20852,7 @@
         <v>76</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>74</v>
@@ -20858,7 +20861,7 @@
         <v>83</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>91</v>
@@ -20866,10 +20869,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20895,13 +20898,13 @@
         <v>125</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20930,10 +20933,10 @@
         <v>141</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>76</v>
@@ -20951,7 +20954,7 @@
         <v>76</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>74</v>
@@ -20968,10 +20971,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20997,13 +21000,13 @@
         <v>258</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -21053,7 +21056,7 @@
         <v>76</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>74</v>
@@ -21070,10 +21073,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21099,13 +21102,13 @@
         <v>98</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -21155,7 +21158,7 @@
         <v>76</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>74</v>
@@ -21172,10 +21175,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21198,19 +21201,19 @@
         <v>76</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>76</v>
@@ -21259,7 +21262,7 @@
         <v>76</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>74</v>
@@ -21271,15 +21274,15 @@
         <v>90</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21376,10 +21379,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21478,14 +21481,14 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -21507,10 +21510,10 @@
         <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N182" t="s" s="2">
         <v>107</v>
@@ -21565,7 +21568,7 @@
         <v>76</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>74</v>
@@ -21582,10 +21585,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21608,16 +21611,16 @@
         <v>76</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -21667,7 +21670,7 @@
         <v>76</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>74</v>
@@ -21676,18 +21679,18 @@
         <v>83</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21710,16 +21713,16 @@
         <v>76</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -21769,27 +21772,27 @@
         <v>76</v>
       </c>
       <c r="AF184" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>751</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21815,16 +21818,16 @@
         <v>282</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>76</v>
@@ -21852,10 +21855,10 @@
         <v>163</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>76</v>
@@ -21873,7 +21876,7 @@
         <v>76</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>74</v>
@@ -21890,10 +21893,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21919,16 +21922,16 @@
         <v>282</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>76</v>
@@ -21956,10 +21959,10 @@
         <v>149</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>76</v>
@@ -21977,7 +21980,7 @@
         <v>76</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>74</v>
@@ -21994,10 +21997,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -22020,19 +22023,19 @@
         <v>76</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>76</v>
@@ -22081,7 +22084,7 @@
         <v>76</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>74</v>
@@ -22093,15 +22096,15 @@
         <v>90</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -22127,10 +22130,10 @@
         <v>98</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>327</v>
@@ -22183,7 +22186,7 @@
         <v>76</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>74</v>
@@ -22200,10 +22203,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -22226,16 +22229,16 @@
         <v>84</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -22285,7 +22288,7 @@
         <v>76</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>74</v>
@@ -22302,10 +22305,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -22328,16 +22331,16 @@
         <v>84</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -22387,7 +22390,7 @@
         <v>76</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>74</v>
@@ -22404,10 +22407,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -22430,19 +22433,19 @@
         <v>84</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>76</v>
@@ -22491,7 +22494,7 @@
         <v>76</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>74</v>
@@ -22508,10 +22511,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22608,10 +22611,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22710,14 +22713,14 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -22739,10 +22742,10 @@
         <v>104</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N194" t="s" s="2">
         <v>107</v>
@@ -22797,7 +22800,7 @@
         <v>76</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>74</v>
@@ -22814,10 +22817,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22843,16 +22846,16 @@
         <v>282</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>76</v>
@@ -22880,10 +22883,10 @@
         <v>149</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>76</v>
@@ -22901,7 +22904,7 @@
         <v>76</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>83</v>
@@ -22918,10 +22921,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22944,19 +22947,19 @@
         <v>84</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>76</v>
@@ -23005,7 +23008,7 @@
         <v>76</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>74</v>
@@ -23022,10 +23025,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -23051,16 +23054,16 @@
         <v>282</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>76</v>
@@ -23088,10 +23091,10 @@
         <v>141</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>76</v>
@@ -23109,7 +23112,7 @@
         <v>76</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>74</v>
@@ -23118,7 +23121,7 @@
         <v>83</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>91</v>
@@ -23126,14 +23129,14 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
@@ -23155,16 +23158,16 @@
         <v>282</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>76</v>
@@ -23192,10 +23195,10 @@
         <v>141</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>76</v>
@@ -23213,7 +23216,7 @@
         <v>76</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>74</v>
@@ -23230,10 +23233,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -23259,16 +23262,16 @@
         <v>77</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>76</v>
@@ -23317,7 +23320,7 @@
         <v>76</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>74</v>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-titer.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
